--- a/1 - 副本.xlsx
+++ b/1 - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="10755"/>
+    <workbookView windowWidth="24000" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1202,7 +1202,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4">
         <v>0</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1351,7 +1351,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3">
